--- a/04_Figures/F04_association/modules/T1/spearman/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T1/spearman/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0107142857142857</v>
+        <v>0.0321428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0386331240489483</v>
+        <v>0.115952634048852</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969769876154569</v>
+        <v>0.909462117094591</v>
       </c>
       <c r="G2" t="n">
         <v>0.969769876154569</v>
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.025</v>
+        <v>0.296428571428571</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0901669634667432</v>
+        <v>1.1190856914849</v>
       </c>
       <c r="F3" t="n">
-        <v>0.929528970819238</v>
+        <v>0.283355428434263</v>
       </c>
       <c r="G3" t="n">
-        <v>0.969769876154569</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.117857142857143</v>
+        <v>0.132142857142857</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.427922350730342</v>
+        <v>0.480662933137168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.675711529221304</v>
+        <v>0.638744218884067</v>
       </c>
       <c r="G4" t="n">
-        <v>0.878424987987696</v>
+        <v>0.878273300965591</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.217857142857143</v>
+        <v>0.0928571428571428</v>
       </c>
       <c r="E5" t="n">
-        <v>0.804826493639811</v>
+        <v>0.33625399478566</v>
       </c>
       <c r="F5" t="n">
-        <v>0.435392673515538</v>
+        <v>0.742045009907367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.797954140108488</v>
+        <v>0.906943900997893</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.375</v>
+        <v>-0.371428571428571</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.45851730441319</v>
+        <v>-1.44239121747272</v>
       </c>
       <c r="F6" t="n">
-        <v>0.168432749846746</v>
+        <v>0.17284974708034</v>
       </c>
       <c r="G6" t="n">
-        <v>0.547406437001923</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.567857142857143</v>
+        <v>0.0107142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>2.48738983495606</v>
+        <v>0.0386331240489483</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0272283567088619</v>
+        <v>0.969769876154569</v>
       </c>
       <c r="G7" t="n">
-        <v>0.353968637215204</v>
+        <v>0.969769876154569</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.235714285714286</v>
+        <v>0.217857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.874521871729162</v>
+        <v>0.804826493639811</v>
       </c>
       <c r="F8" t="n">
-        <v>0.397702945903273</v>
+        <v>0.435392673515538</v>
       </c>
       <c r="G8" t="n">
-        <v>0.797954140108488</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.132142857142857</v>
+        <v>0.235714285714286</v>
       </c>
       <c r="E9" t="n">
-        <v>0.480662933137168</v>
+        <v>0.874521871729162</v>
       </c>
       <c r="F9" t="n">
-        <v>0.638744218884067</v>
+        <v>0.397702945903273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.878424987987696</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.025</v>
+        <v>0.253571428571429</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0901669634667432</v>
+        <v>0.945155625533198</v>
       </c>
       <c r="F10" t="n">
-        <v>0.929528970819238</v>
+        <v>0.36181610381589</v>
       </c>
       <c r="G10" t="n">
-        <v>0.969769876154569</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.407142857142857</v>
+        <v>-0.225</v>
       </c>
       <c r="E11" t="n">
-        <v>1.60721646388664</v>
+        <v>-0.832597876032085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.132012663779854</v>
+        <v>0.420104686907635</v>
       </c>
       <c r="G11" t="n">
-        <v>0.547406437001923</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.442857142857143</v>
+        <v>-0.203571428571429</v>
       </c>
       <c r="E12" t="n">
-        <v>1.78090346782642</v>
+        <v>-0.749685567013641</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0982940655468714</v>
+        <v>0.466795072489112</v>
       </c>
       <c r="G12" t="n">
-        <v>0.547406437001923</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.232142857142857</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.860510661125327</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.405098740693649</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.797954140108488</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.192857142857143</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.708660102968926</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.491048701605223</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.797954140108488</v>
+        <v>0.733535113911462</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.146428571428571</v>
+        <v>0.0178571428571429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.533708434419441</v>
+        <v>0.064395112101152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.602549920983054</v>
+        <v>0.949635304173862</v>
       </c>
       <c r="G2" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.103571428571429</v>
+        <v>0.103571428571429</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.375451266447069</v>
+        <v>0.375451266447069</v>
       </c>
       <c r="F3" t="n">
         <v>0.713379630628729</v>
       </c>
       <c r="G3" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0857142857142857</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.310188821950692</v>
+        <v>-0.180503334135647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.761334126190767</v>
+        <v>0.859540943467457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0428571428571429</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="E5" t="n">
-        <v>0.154665731331055</v>
+        <v>-0.128851890580845</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8794603130259</v>
+        <v>0.899446993472087</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8794603130259</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.135714285714286</v>
+        <v>-0.107142857142857</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.493894317922737</v>
+        <v>-0.38854567548164</v>
       </c>
       <c r="F6" t="n">
-        <v>0.629620441872815</v>
+        <v>0.703901001626162</v>
       </c>
       <c r="G6" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.475</v>
+        <v>0.146428571428571</v>
       </c>
       <c r="E7" t="n">
-        <v>1.94620966033193</v>
+        <v>0.533708434419441</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0735708620459136</v>
+        <v>0.602549920983054</v>
       </c>
       <c r="G7" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.221428571428571</v>
+        <v>0.239285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.818694863860519</v>
+        <v>0.888570600065875</v>
       </c>
       <c r="F8" t="n">
-        <v>0.42771371901637</v>
+        <v>0.390379311920236</v>
       </c>
       <c r="G8" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.221428571428571</v>
+        <v>0.146428571428571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.818694863860519</v>
+        <v>0.533708434419441</v>
       </c>
       <c r="F9" t="n">
-        <v>0.42771371901637</v>
+        <v>0.602549920983054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0928571428571428</v>
+        <v>0.0464285714285714</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.33625399478566</v>
+        <v>0.16758131253873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.742045009907367</v>
+        <v>0.869491525545095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.285714285714286</v>
+        <v>-0.075</v>
       </c>
       <c r="E11" t="n">
-        <v>1.07496769977314</v>
+        <v>-0.271180115299783</v>
       </c>
       <c r="F11" t="n">
-        <v>0.301936351322549</v>
+        <v>0.790510794155268</v>
       </c>
       <c r="G11" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0892857142857143</v>
+        <v>-0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.323215124514436</v>
+        <v>-0.735980072193987</v>
       </c>
       <c r="F12" t="n">
-        <v>0.751672517350277</v>
+        <v>0.474813964522168</v>
       </c>
       <c r="G12" t="n">
-        <v>0.877617886936389</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0678571428571429</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.245227646009749</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.810108818710513</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.877617886936389</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0928571428571428</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.33625399478566</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.742045009907367</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.877617886936389</v>
+        <v>0.949635304173862</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.157142857142857</v>
+        <v>0.128571428571429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.573714526046661</v>
+        <v>0.467450600950195</v>
       </c>
       <c r="F2" t="n">
-        <v>0.575952600603795</v>
+        <v>0.647916329466507</v>
       </c>
       <c r="G2" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.235714285714286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0515131320740328</v>
+        <v>0.874521871729162</v>
       </c>
       <c r="F3" t="n">
-        <v>0.959699764598948</v>
+        <v>0.397702945903273</v>
       </c>
       <c r="G3" t="n">
-        <v>0.959699764598948</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.203571428571429</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.749685567013641</v>
+        <v>-0.180503334135647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.466795072489112</v>
+        <v>0.859540943467457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167857142857143</v>
+        <v>-0.0714285714285714</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6139283620727</v>
+        <v>-0.258198889747161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.549855554227802</v>
+        <v>0.800295987397054</v>
       </c>
       <c r="G5" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.260714285714286</v>
+        <v>-0.235714285714286</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.973692917115073</v>
+        <v>-0.874521871729162</v>
       </c>
       <c r="F6" t="n">
-        <v>0.347979459862794</v>
+        <v>0.397702945903273</v>
       </c>
       <c r="G6" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.582142857142857</v>
+        <v>0.157142857142857</v>
       </c>
       <c r="E7" t="n">
-        <v>2.58145457059098</v>
+        <v>0.573714526046661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0227936871264143</v>
+        <v>0.575952600603795</v>
       </c>
       <c r="G7" t="n">
-        <v>0.296317932643385</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.289285714285714</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>1.08962373769732</v>
+        <v>1.30045037243686</v>
       </c>
       <c r="F8" t="n">
-        <v>0.295665361004378</v>
+        <v>0.216028925341955</v>
       </c>
       <c r="G8" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.271428571428571</v>
+        <v>0.221428571428571</v>
       </c>
       <c r="E9" t="n">
-        <v>1.01682258925182</v>
+        <v>0.818694863860519</v>
       </c>
       <c r="F9" t="n">
-        <v>0.327789306841173</v>
+        <v>0.42771371901637</v>
       </c>
       <c r="G9" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.135714285714286</v>
+        <v>0.103571428571429</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.493894317922737</v>
+        <v>0.375451266447069</v>
       </c>
       <c r="F10" t="n">
-        <v>0.629620441872815</v>
+        <v>0.713379630628729</v>
       </c>
       <c r="G10" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.414285714285714</v>
+        <v>-0.171428571428571</v>
       </c>
       <c r="E11" t="n">
-        <v>1.64119486093802</v>
+        <v>-0.627381920373686</v>
       </c>
       <c r="F11" t="n">
-        <v>0.124715442236571</v>
+        <v>0.541272176099633</v>
       </c>
       <c r="G11" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.242857142857143</v>
+        <v>-0.317857142857143</v>
       </c>
       <c r="E12" t="n">
-        <v>0.90265758615802</v>
+        <v>-1.20873699952121</v>
       </c>
       <c r="F12" t="n">
-        <v>0.383128341839342</v>
+        <v>0.248290565817018</v>
       </c>
       <c r="G12" t="n">
-        <v>0.682088812028882</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.547021696619878</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.593630202742588</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.682088812028882</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.153571428571429</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.560356865859059</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.584764094941016</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.682088812028882</v>
+        <v>0.859540943467457</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.210714285714286</v>
+        <v>-0.242857142857143</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.777190891009981</v>
+        <v>-0.90265758615802</v>
       </c>
       <c r="F2" t="n">
-        <v>0.450957865215285</v>
+        <v>0.383128341839342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.837493178256958</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.075</v>
+        <v>0.314285714285714</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.271180115299783</v>
+        <v>1.19365775688834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.790510794155268</v>
+        <v>0.253940016323672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.889445929673949</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.146428571428571</v>
+        <v>0.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.533708434419441</v>
+        <v>0.735980072193987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.602549920983054</v>
+        <v>0.474813964522168</v>
       </c>
       <c r="G4" t="n">
-        <v>0.889445929673949</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.371428571428571</v>
+        <v>0.382142857142857</v>
       </c>
       <c r="E5" t="n">
-        <v>1.44239121747272</v>
+        <v>1.49099751546869</v>
       </c>
       <c r="F5" t="n">
-        <v>0.17284974708034</v>
+        <v>0.159823629986967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.669161974304041</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.371428571428571</v>
+        <v>-0.417857142857143</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.44239121747272</v>
+        <v>-1.65832054902412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.17284974708034</v>
+        <v>0.121172536021878</v>
       </c>
       <c r="G6" t="n">
-        <v>0.669161974304041</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0392857142857143</v>
+        <v>-0.210714285714286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.141756090351083</v>
+        <v>-0.777190891009981</v>
       </c>
       <c r="F7" t="n">
-        <v>0.889445929673949</v>
+        <v>0.450957865215285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.889445929673949</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.267857142857143</v>
+        <v>-0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0024017876421</v>
+        <v>-0.547021696619878</v>
       </c>
       <c r="F8" t="n">
-        <v>0.334443600512354</v>
+        <v>0.593630202742588</v>
       </c>
       <c r="G8" t="n">
-        <v>0.783934891601094</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.253571428571429</v>
+        <v>-0.107142857142857</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.945155625533198</v>
+        <v>-0.38854567548164</v>
       </c>
       <c r="F9" t="n">
-        <v>0.36181610381589</v>
+        <v>0.703901001626162</v>
       </c>
       <c r="G9" t="n">
-        <v>0.783934891601094</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.346428571428571</v>
+        <v>0.167857142857143</v>
       </c>
       <c r="E10" t="n">
-        <v>1.33151845580652</v>
+        <v>0.6139283620727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.205895992093551</v>
+        <v>0.549855554227802</v>
       </c>
       <c r="G10" t="n">
-        <v>0.669161974304041</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.103571428571429</v>
+        <v>-0.0785714285714286</v>
       </c>
       <c r="E11" t="n">
-        <v>0.375451266447069</v>
+        <v>-0.284171835544338</v>
       </c>
       <c r="F11" t="n">
-        <v>0.713379630628729</v>
+        <v>0.780754552309047</v>
       </c>
       <c r="G11" t="n">
-        <v>0.889445929673949</v>
+        <v>0.780754552309047</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.557142857142857</v>
+        <v>0.117857142857143</v>
       </c>
       <c r="E12" t="n">
-        <v>2.41903519640459</v>
+        <v>0.427922350730342</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0309610867558121</v>
+        <v>0.675711529221304</v>
       </c>
       <c r="G12" t="n">
-        <v>0.402494127825557</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0857142857142857</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.310188821950692</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.761334126190767</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.889445929673949</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.180503334135647</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.859540943467457</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.889445929673949</v>
+        <v>0.774291101788778</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.279571688265735</v>
+        <v>0.38351500826197</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0498739701227</v>
+        <v>1.49727250230288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.312902260302947</v>
+        <v>0.158203956879739</v>
       </c>
       <c r="G2" t="n">
-        <v>0.708256702937541</v>
+        <v>0.471413343185833</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.157707106201184</v>
+        <v>0.093190562755245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.575826995285178</v>
+        <v>0.337471932108231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.574565535775215</v>
+        <v>0.741147994563553</v>
       </c>
       <c r="G3" t="n">
-        <v>0.770226732043002</v>
+        <v>0.741147994563553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.172044115855837</v>
+        <v>-0.200718135165143</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.629703231460603</v>
+        <v>-0.738733467789151</v>
       </c>
       <c r="F4" t="n">
-        <v>0.539798780972483</v>
+        <v>0.473196226117344</v>
       </c>
       <c r="G4" t="n">
-        <v>0.770226732043002</v>
+        <v>0.650644810911348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0860220579279185</v>
+        <v>-0.480289823430878</v>
       </c>
       <c r="E5" t="n">
-        <v>0.311310897731823</v>
+        <v>-1.97433604166662</v>
       </c>
       <c r="F5" t="n">
-        <v>0.760500214375172</v>
+        <v>0.0699777664427422</v>
       </c>
       <c r="G5" t="n">
-        <v>0.770226732043002</v>
+        <v>0.471413343185833</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.347672484125337</v>
+        <v>0.340503979298011</v>
       </c>
       <c r="E6" t="n">
-        <v>1.33695554610092</v>
+        <v>1.30573102796929</v>
       </c>
       <c r="F6" t="n">
-        <v>0.204162957944674</v>
+        <v>0.214278792357197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.708256702937541</v>
+        <v>0.471413343185833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.125448834478214</v>
+        <v>0.279571688265735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.455913883495559</v>
+        <v>1.0498739701227</v>
       </c>
       <c r="F7" t="n">
-        <v>0.655974483832517</v>
+        <v>0.312902260302947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.770226732043002</v>
+        <v>0.533308450004438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.261650426197419</v>
+        <v>0.36200949377999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.977445584349582</v>
+        <v>1.40021414578119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.346188266964246</v>
+        <v>0.184861346373565</v>
       </c>
       <c r="G8" t="n">
-        <v>0.708256702937541</v>
+        <v>0.471413343185833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>0.379930755848307</v>
+        <v>0.111111824823561</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4809056339304</v>
+        <v>0.403115509142425</v>
       </c>
       <c r="F9" t="n">
-        <v>0.162457893036478</v>
+        <v>0.693414598172773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.708256702937541</v>
+        <v>0.741147994563553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.505379590326521</v>
+        <v>-0.412189027571276</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.11169089290171</v>
+        <v>-1.63118358423432</v>
       </c>
       <c r="F10" t="n">
-        <v>0.054639943597371</v>
+        <v>0.126828099845018</v>
       </c>
       <c r="G10" t="n">
-        <v>0.708256702937541</v>
+        <v>0.471413343185833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>0.272403183438409</v>
+        <v>-0.132617339305541</v>
       </c>
       <c r="E11" t="n">
-        <v>1.02076574189301</v>
+        <v>-0.482419679164531</v>
       </c>
       <c r="F11" t="n">
-        <v>0.325986623185301</v>
+        <v>0.637529271456666</v>
       </c>
       <c r="G11" t="n">
-        <v>0.708256702937541</v>
+        <v>0.741147994563553</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0860220579279185</v>
+        <v>-0.265234678611082</v>
       </c>
       <c r="E12" t="n">
-        <v>0.311310897731823</v>
+        <v>-0.991841129104247</v>
       </c>
       <c r="F12" t="n">
-        <v>0.760500214375172</v>
+        <v>0.339378104548279</v>
       </c>
       <c r="G12" t="n">
-        <v>0.770226732043002</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.0824378055142552</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.298248911115087</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.770226732043002</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.770226732043002</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.243729164129102</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.906103044511344</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.381368993889445</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.708256702937541</v>
+        <v>0.533308450004438</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.156388044567705</v>
+        <v>0.0748900495112955</v>
       </c>
       <c r="E2" t="n">
-        <v>0.548492903529079</v>
+        <v>0.260157315962355</v>
       </c>
       <c r="F2" t="n">
-        <v>0.593411482796674</v>
+        <v>0.79915261522139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.754667787086879</v>
+        <v>0.879067876743529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.123348316842134</v>
+        <v>0.244493985169229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.430579248802022</v>
+        <v>0.873460838825014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.67440656570597</v>
+        <v>0.39955406085224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.754667787086879</v>
+        <v>0.62787066705352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.114537722781981</v>
+        <v>0.308370792105334</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.399398794051085</v>
+        <v>1.12295350859831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.696616418849427</v>
+        <v>0.283422348510189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.754667787086879</v>
+        <v>0.623529166722416</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.262115173289534</v>
+        <v>0.244493985169229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.94089032147157</v>
+        <v>0.873460838825014</v>
       </c>
       <c r="F5" t="n">
-        <v>0.365316570631064</v>
+        <v>0.39955406085224</v>
       </c>
       <c r="G5" t="n">
-        <v>0.678445059743404</v>
+        <v>0.62787066705352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.539648886184335</v>
+        <v>-0.458150891127925</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2204779397206</v>
+        <v>-1.7854954307151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0463985985648553</v>
+        <v>0.0994566118960853</v>
       </c>
       <c r="G6" t="n">
-        <v>0.30159089067156</v>
+        <v>0.364674243618979</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.367842302011363</v>
+        <v>0.156388044567705</v>
       </c>
       <c r="E7" t="n">
-        <v>1.37031863608769</v>
+        <v>0.548492903529079</v>
       </c>
       <c r="F7" t="n">
-        <v>0.195677967907994</v>
+        <v>0.593411482796674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.58319778681704</v>
+        <v>0.764314765137152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>0.317181386165487</v>
+        <v>-0.0264317821804572</v>
       </c>
       <c r="E8" t="n">
-        <v>1.15857151761105</v>
+        <v>-0.0915943806408584</v>
       </c>
       <c r="F8" t="n">
-        <v>0.269168209300172</v>
+        <v>0.928531584478003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.58319778681704</v>
+        <v>0.928531584478003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0044052970300762</v>
+        <v>0.361234356466249</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0152605446357296</v>
+        <v>1.34196888451332</v>
       </c>
       <c r="F9" t="n">
-        <v>0.988075108981028</v>
+        <v>0.204446709706075</v>
       </c>
       <c r="G9" t="n">
-        <v>0.988075108981028</v>
+        <v>0.562228451691707</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>0.22026485150381</v>
+        <v>0.711455470357307</v>
       </c>
       <c r="E10" t="n">
-        <v>0.782231348951682</v>
+        <v>3.50710785038474</v>
       </c>
       <c r="F10" t="n">
-        <v>0.449239070749437</v>
+        <v>0.00432487925868763</v>
       </c>
       <c r="G10" t="n">
-        <v>0.730013489967835</v>
+        <v>0.0475736718455639</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.121145668327096</v>
+        <v>-0.607930990150516</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.422774751285465</v>
+        <v>-2.65234458087168</v>
       </c>
       <c r="F11" t="n">
-        <v>0.679936775014068</v>
+        <v>0.0210875297816255</v>
       </c>
       <c r="G11" t="n">
-        <v>0.754667787086879</v>
+        <v>0.11598141379894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>0.334802574285791</v>
+        <v>-0.143172153477477</v>
       </c>
       <c r="E12" t="n">
-        <v>1.23082303047882</v>
+        <v>-0.501125584315583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.241969067707667</v>
+        <v>0.625348444203125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.58319778681704</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.634362772330973</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-2.84268591128162</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.014822639376478</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.192694311894215</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.44052970300762</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.69987189469006</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.114904490247227</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.497919457737985</v>
+        <v>0.764314765137152</v>
       </c>
     </row>
   </sheetData>
@@ -2454,48 +2172,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2506,45 +2224,45 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.262115173289534</v>
+        <v>0.244493985169229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2553,24 +2271,24 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.243729164129102</v>
+        <v>0.279571688265735</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2584,54 +2302,54 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.203571428571429</v>
+        <v>0.171428571428571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.210714285714286</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
